--- a/docs/samples/timetable-import-sample.xlsx
+++ b/docs/samples/timetable-import-sample.xlsx
@@ -6,14 +6,27 @@
   <sheets>
     <sheet sheetId="1" name="10A1" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="10A2" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Huong_dan" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="10A3" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="10A4" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="10A5" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="11A1" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="11A2" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="11A3" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="11A4" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="11A5" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="12A1" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="12A2" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="12A3" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="12A4" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="12A5" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Huong_dan" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="258">
   <si>
     <t>THỜI KHÓA BIỂU</t>
   </si>
@@ -27,7 +40,7 @@
     <t>Năm học</t>
   </si>
   <si>
-    <t>2025-2026</t>
+    <t>2026-2027</t>
   </si>
   <si>
     <t>Học kỳ</t>
@@ -39,7 +52,13 @@
     <t>Số tiết</t>
   </si>
   <si>
-    <t>4</t>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Khối đầu cấp — gợi ý mã môn từ phân công</t>
   </si>
   <si>
     <t>Tiết</t>
@@ -60,54 +79,862 @@
     <t>Thứ 6</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOAN-10A1
-tranvanhung.import@demo.edu.vn
+    <t>1 (Sáng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">LY-10A1
-phamvanminh.import@demo.edu.vn
-P.201</t>
+    <t xml:space="preserve">TIN
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.101</t>
+  </si>
+  <si>
+    <t>2 (Sáng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.101</t>
+  </si>
+  <si>
+    <t>3 (Sáng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.101</t>
+  </si>
+  <si>
+    <t>4 (Sáng)</t>
+  </si>
+  <si>
+    <t>5 (Sáng)</t>
+  </si>
+  <si>
+    <t>6 (Chiều)</t>
+  </si>
+  <si>
+    <t>7 (Chiều)</t>
+  </si>
+  <si>
+    <t>8 (Chiều)</t>
+  </si>
+  <si>
+    <t>9 (Chiều)</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAN-10A1
-nguyenthilan.import@demo.edu.vn
-P.101</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANH-10A1
-lethimai.import@demo.edu.vn
+    <t>10 (Chiều)</t>
+  </si>
+  <si>
+    <t>10A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
 P.102</t>
   </si>
   <si>
-    <t>10A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOAN-10A2
-tranvanhung.import@demo.edu.vn
+    <t xml:space="preserve">TD
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.102</t>
+  </si>
+  <si>
+    <t>10A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN-10A2
-nguyenthilan.import@demo.edu.vn
+    <t xml:space="preserve">CN
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA-10A2
-lethimai.import@demo.edu.vn
-P.LAB1</t>
+    <t xml:space="preserve">SINH
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.103</t>
+  </si>
+  <si>
+    <t>10A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.104</t>
+  </si>
+  <si>
+    <t>10A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.105</t>
+  </si>
+  <si>
+    <t>11A1</t>
+  </si>
+  <si>
+    <t>Đã điền từ TKB HK2 năm trước (chỉ mã môn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.106</t>
+  </si>
+  <si>
+    <t>11A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.107</t>
+  </si>
+  <si>
+    <t>11A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.108</t>
+  </si>
+  <si>
+    <t>11A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.109</t>
+  </si>
+  <si>
+    <t>11A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.110</t>
+  </si>
+  <si>
+    <t>12A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.111</t>
+  </si>
+  <si>
+    <t>12A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.112</t>
+  </si>
+  <si>
+    <t>12A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.113</t>
+  </si>
+  <si>
+    <t>12A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.114</t>
+  </si>
+  <si>
+    <t>12A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOA
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GKTPL
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANH
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINH
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOAN
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIN
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LY
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDQP
+P.115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU
+P.115</t>
   </si>
   <si>
     <t>Hướng dẫn import thời khóa biểu (TKB)</t>
@@ -125,16 +952,19 @@
     <t>- Dòng header: Tiết | Thứ 2 | Thứ 3 | Thứ 4 | Thứ 5 | Thứ 6</t>
   </si>
   <si>
-    <t>Nội dung mỗi ô (3 dòng):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dòng 1: ma_lop_mon (vd. VAN-10A2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dòng 2: email_gv (vd. gv.van@demo.edu.vn)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dòng 3: phòng học (tuỳ chọn, vd. P.101)</t>
+    <t>- Mỗi ngày có 10 tiết: 1–5 sáng, 6–10 chiều</t>
+  </si>
+  <si>
+    <t>Nội dung mỗi ô:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dòng 1 (bắt buộc): mã môn (TOAN) hoặc tên môn (Toán học) hoặc mã lớp môn (TOAN-10A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Dòng 2 (tuỳ chọn): phòng học (vd. P.101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Không cần ghi giáo viên — hệ thống lấy GV từ phân công lớp môn</t>
   </si>
   <si>
     <t>Quy tắc:</t>
@@ -146,19 +976,25 @@
     <t>- Import vào học kỳ đã chọn trên form</t>
   </si>
   <si>
-    <t>- GV phải đã được phân công lớp môn tương ứng</t>
+    <t>- Lớp môn phải đã tồn tại và đã có phân công GV ACTIVE</t>
   </si>
   <si>
     <t>- Không trùng tiết trong cùng lớp môn hoặc lịch GV</t>
   </si>
   <si>
-    <t>- Chế độ replace: xóa TKB cũ của từng lớp HC trong file rồi ghi mới</t>
-  </si>
-  <si>
-    <t>- Chế độ merge: giữ tiết cũ, cập nhật/thêm tiết có trong file</t>
-  </si>
-  <si>
-    <t>- File mẫu tham khảo: docs/samples/timetable-import-sample.xlsx</t>
+    <t>- Import ghi đè TKB cũ của từng lớp HC có trong file (ô trống = không tạo tiết)</t>
+  </si>
+  <si>
+    <t>Tải mẫu kèm học kỳ:</t>
+  </si>
+  <si>
+    <t>- Khối 11/12: ưu tiên TKB ACTIVE HK2 năm trước</t>
+  </si>
+  <si>
+    <t>- Khối 10 hoặc thiếu TKB năm trước: gợi ý lịch từ lớp môn đã phân công</t>
+  </si>
+  <si>
+    <t>File mẫu tham khảo: docs/samples/timetable-import-sample.xlsx</t>
   </si>
 </sst>
 </file>
@@ -558,10 +1394,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -623,94 +1459,2264 @@
       <c r="E5"/>
       <c r="F5"/>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F11" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="F14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>18</v>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -718,10 +3724,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -740,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -776,80 +3782,253 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
       <c r="F5"/>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -858,113 +4037,2190 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="80" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>43</v>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="6" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/samples/timetable-import-sample.xlsx
+++ b/docs/samples/timetable-import-sample.xlsx
@@ -82,61 +82,61 @@
     <t>1 (Sáng)</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.101</t>
   </si>
   <si>
     <t>2 (Sáng)</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.101</t>
   </si>
   <si>
     <t>3 (Sáng)</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.101</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.101</t>
   </si>
   <si>
@@ -167,220 +167,220 @@
     <t>10A2</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.102</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.102</t>
   </si>
   <si>
     <t>10A3</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.103</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.103</t>
   </si>
   <si>
     <t>10A4</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.104</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.104</t>
   </si>
   <si>
     <t>10A5</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.105</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.105</t>
   </si>
   <si>
@@ -390,550 +390,550 @@
     <t>Đã điền từ TKB HK2 năm trước (chỉ mã môn)</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.106</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.106</t>
   </si>
   <si>
     <t>11A2</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.107</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.107</t>
   </si>
   <si>
     <t>11A3</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.108</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.108</t>
   </si>
   <si>
     <t>11A4</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.109</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.109</t>
   </si>
   <si>
     <t>11A5</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.110</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.110</t>
   </si>
   <si>
     <t>12A1</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.111</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.111</t>
   </si>
   <si>
     <t>12A2</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.112</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.112</t>
   </si>
   <si>
     <t>12A3</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.113</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.113</t>
   </si>
   <si>
     <t>12A4</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.114</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.114</t>
   </si>
   <si>
     <t>12A5</t>
   </si>
   <si>
-    <t xml:space="preserve">VAN
+    <t xml:space="preserve">Ngữ văn
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">TD
+    <t xml:space="preserve">Giáo dục thể chất
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">HOA
+    <t xml:space="preserve">Hóa học
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">GKTPL
+    <t xml:space="preserve">Giáo dục kinh tế và pháp luật
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">DIA
+    <t xml:space="preserve">Địa lý
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">ANH
+    <t xml:space="preserve">Tiếng Anh
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">CN
+    <t xml:space="preserve">Công nghệ
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">SINH
+    <t xml:space="preserve">Sinh học
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">TOAN
+    <t xml:space="preserve">Toán học
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">TIN
+    <t xml:space="preserve">Tin học
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">LY
+    <t xml:space="preserve">Vật lý
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">GDQP
+    <t xml:space="preserve">Giáo dục quốc phòng và an ninh
 P.115</t>
   </si>
   <si>
-    <t xml:space="preserve">SU
+    <t xml:space="preserve">Lịch sử
 P.115</t>
   </si>
   <si>
@@ -964,7 +964,7 @@
     <t xml:space="preserve">  Dòng 2 (tuỳ chọn): phòng học (vd. P.101)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Không cần ghi giáo viên — hệ thống lấy GV từ phân công lớp môn</t>
+    <t xml:space="preserve">  Không cần ghi giáo viên — hệ thống đối chiếu Phân công giảng dạy (ACTIVE) theo lớp HC + môn</t>
   </si>
   <si>
     <t>Quy tắc:</t>
@@ -976,7 +976,7 @@
     <t>- Import vào học kỳ đã chọn trên form</t>
   </si>
   <si>
-    <t>- Lớp môn phải đã tồn tại và đã có phân công GV ACTIVE</t>
+    <t>- Ô có môn nhưng chưa phân công GV → bỏ qua (không báo lỗi)</t>
   </si>
   <si>
     <t>- Không trùng tiết trong cùng lớp môn hoặc lịch GV</t>
